--- a/d2b2/D2B2_기획_문서/003_시스템_기획서/004_튜토리얼/Project_D2B2_시스템기획서_튜토리얼.xlsx
+++ b/d2b2/D2B2_기획_문서/003_시스템_기획서/004_튜토리얼/Project_D2B2_시스템기획서_튜토리얼.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="201">
   <si>
     <t>튜토리얼 시스템 기획</t>
   </si>
@@ -624,6 +624,10 @@
   </si>
   <si>
     <t>등등등.....</t>
+  </si>
+  <si>
+    <t>작성자: 양서연</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4091,7 +4095,9 @@
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
+      <c r="X5" s="10" t="s">
+        <v>200</v>
+      </c>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
